--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56357500</v>
+        <v>103997268</v>
       </c>
       <c r="B2" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6437</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Pikhöjden, Ö om, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569387.9206501753</v>
+        <v>569455</v>
       </c>
       <c r="R2" t="n">
-        <v>7011499.009428301</v>
+        <v>7011232</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,47 +767,34 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>250-årig ljus tallskog på torr moränbacke</t>
-        </is>
-      </c>
-      <c r="AN2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>1 substratenheter # tallhögstubbe, grov</t>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56357502</v>
+        <v>103997255</v>
       </c>
       <c r="B3" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,37 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6487</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Pikhöjden, Ö om, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>569387.9206501753</v>
+        <v>569437</v>
       </c>
       <c r="R3" t="n">
-        <v>7011499.009428301</v>
+        <v>7011228</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,22 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,47 +883,34 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>250-årig ljus tallskog på torr moränbacke</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # tallhögstubbe, grov</t>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Via Johan Staaf</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>SCA Skog Naturvärdesinventering</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>97362342</v>
+        <v>103997200</v>
       </c>
       <c r="B4" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,34 +918,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6487</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Halbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>569409.9964892997</v>
+        <v>569436</v>
       </c>
       <c r="R4" t="n">
-        <v>7011480.541820726</v>
+        <v>7011235</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1003,22 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2022-08-13</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,9 +999,9 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Tallhögstubbe</t>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1048,21 +1017,16 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2021</t>
+          <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103997268</v>
+        <v>103997249</v>
       </c>
       <c r="B5" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1094,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>569455.0910610332</v>
+        <v>569457</v>
       </c>
       <c r="R5" t="n">
-        <v>7011232.090140134</v>
+        <v>7011229</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1175,15 +1139,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103997255</v>
+        <v>56357500</v>
       </c>
       <c r="B6" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1191,37 +1150,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Pikhöjden, Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569437.1200043693</v>
+        <v>569388</v>
       </c>
       <c r="R6" t="n">
-        <v>7011227.643688506</v>
+        <v>7011499</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1245,22 +1204,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1272,39 +1221,42 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>250-årig ljus tallskog på torr moränbacke</t>
+        </is>
+      </c>
+      <c r="AN6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tallhögstubbe, grov</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103997200</v>
+        <v>56357502</v>
       </c>
       <c r="B7" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1312,37 +1264,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Pikhöjden, Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>569436.0617749451</v>
+        <v>569388</v>
       </c>
       <c r="R7" t="n">
-        <v>7011234.83774999</v>
+        <v>7011499</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,22 +1318,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:22</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1393,39 +1335,42 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>250-årig ljus tallskog på torr moränbacke</t>
+        </is>
+      </c>
+      <c r="AN7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>1 substratenheter # tallhögstubbe, grov</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Johan Staaf</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103997249</v>
+        <v>97362342</v>
       </c>
       <c r="B8" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,34 +1378,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Halbodarna, Jmt</t>
+          <t>Nissemyran, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569457.4163309387</v>
+        <v>569410</v>
       </c>
       <c r="R8" t="n">
-        <v>7011228.982846403</v>
+        <v>7011480</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1487,22 +1432,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-08-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2021-06-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,9 +1449,9 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Jesper Wadstein</t>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1532,7 +1467,7 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>LstZ inventering av skogliga värdetrakter 2022</t>
+          <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997268</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997255</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997200</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103997249</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357500</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1364,6 +1394,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357502</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1470,8 +1505,22 @@
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97362342</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56357500</v>
+        <v>135641255</v>
       </c>
       <c r="B6" t="n">
-        <v>78730</v>
+        <v>92016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,37 +1175,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pikhöjden, Ö om, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569388</v>
+        <v>569530</v>
       </c>
       <c r="R6" t="n">
-        <v>7011499</v>
+        <v>7011165</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,47 +1246,45 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>250-årig ljus tallskog på torr moränbacke</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # tallhögstubbe, grov</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357500</t>
+          <t>https://artportalen.se/Sighting/135641255</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56357502</v>
+        <v>56357500</v>
       </c>
       <c r="B7" t="n">
-        <v>78334</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,21 +1292,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1396,13 +1394,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357502</t>
+          <t>https://artportalen.se/Sighting/56357500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97362342</v>
+        <v>56357502</v>
       </c>
       <c r="B8" t="n">
         <v>78334</v>
@@ -1433,17 +1431,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Pikhöjden, Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569410</v>
+        <v>569388</v>
       </c>
       <c r="R8" t="n">
-        <v>7011480</v>
+        <v>7011499</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,12 +1465,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,30 +1482,358 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>250-årig ljus tallskog på torr moränbacke</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Tallhögstubbe</t>
+          <t>1 substratenheter # tallhögstubbe, grov</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357502</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97362342</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>569410</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7011480</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Via Johan Staaf</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/97362342</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135641256</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>569508</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7011154</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641256</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135641254</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>569558</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7011204</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641254</t>
         </is>
       </c>
     </row>
@@ -1520,6 +1846,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>135641255</v>
       </c>
       <c r="B6" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135641254</v>
       </c>
       <c r="B11" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56357500</v>
+        <v>135641255</v>
       </c>
       <c r="B6" t="n">
-        <v>78730</v>
+        <v>92048</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,37 +1175,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Pikhöjden, Ö om, Jmt</t>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>569388</v>
+        <v>569530</v>
       </c>
       <c r="R6" t="n">
-        <v>7011499</v>
+        <v>7011165</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-10-08</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,47 +1246,45 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>250-årig ljus tallskog på torr moränbacke</t>
-        </is>
-      </c>
-      <c r="AN6" t="n">
-        <v>1</v>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>1 substratenheter # tallhögstubbe, grov</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Carl Jansson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357500</t>
+          <t>https://artportalen.se/Sighting/135641255</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56357502</v>
+        <v>56357500</v>
       </c>
       <c r="B7" t="n">
-        <v>78334</v>
+        <v>78730</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,21 +1292,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1396,13 +1394,13 @@
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/56357502</t>
+          <t>https://artportalen.se/Sighting/56357500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>97362342</v>
+        <v>56357502</v>
       </c>
       <c r="B8" t="n">
         <v>78334</v>
@@ -1433,17 +1431,17 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nissemyran, Jmt</t>
+          <t>Pikhöjden, Ö om, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>569410</v>
+        <v>569388</v>
       </c>
       <c r="R8" t="n">
-        <v>7011480</v>
+        <v>7011499</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1467,12 +1465,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-06-17</t>
+          <t>2015-10-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,30 +1482,358 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>250-årig ljus tallskog på torr moränbacke</t>
+        </is>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Tallhögstubbe</t>
+          <t>1 substratenheter # tallhögstubbe, grov</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56357502</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>97362342</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Nissemyran, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>569410</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7011480</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-06-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Tallhögstubbe</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Johan Staaf</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Via Johan Staaf</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr">
+      <c r="AY9" t="inlineStr">
         <is>
           <t>LstZ inventering av skogliga värdetrakter 2021</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
+      <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/97362342</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>135641256</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>569508</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7011154</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641256</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135641254</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99274</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Halbodarna, Hammarstrand, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>569558</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7011204</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135641254</t>
         </is>
       </c>
     </row>
@@ -1520,6 +1846,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>135641255</v>
       </c>
       <c r="B6" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135641254</v>
       </c>
       <c r="B11" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>135641255</v>
       </c>
       <c r="B6" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>135641256</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135641254</v>
       </c>
       <c r="B11" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>135641255</v>
       </c>
       <c r="B6" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135641254</v>
       </c>
       <c r="B11" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>135641255</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135641254</v>
       </c>
       <c r="B11" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>135641255</v>
       </c>
       <c r="B6" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>135641256</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135641254</v>
       </c>
       <c r="B11" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 43106-2023 artfynd.xlsx
+++ b/artfynd/A 43106-2023 artfynd.xlsx
@@ -1167,7 +1167,7 @@
         <v>135641255</v>
       </c>
       <c r="B6" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>135641256</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>135641254</v>
       </c>
       <c r="B11" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
